--- a/inputs/CEREBRO_Input_Temozolomide.xlsx
+++ b/inputs/CEREBRO_Input_Temozolomide.xlsx
@@ -787,14 +787,14 @@
     <row r="1" ht="38" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
-          <t>CEREBRO-X v22.1   ⟶   Drug Input  (Validation Set: 3 drug types)</t>
+          <t>CEREBRO-X v22.1   ⟶   Drug Input  (Temozolomide — small molecule, glioblastoma)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3-drug validation: monoclonal antibody + small molecule + antisense oligonucleotide. Tests all FDA categories the pipeline must support.</t>
+          <t>Single-drug validation: DNA-alkylating small molecule, GBM standard-of-care.</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Lecanemab</t>
+          <t>Temozolomide</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>monoclonal_antibody</t>
+          <t>small_molecule</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -894,8 +894,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>&gt;Lecanemab_VH
-QVQLVQSGAEVKKPGSSVKVSCKASGYTFTNYGMNWVRQAPGQGLEWMGWINTYTGEPTYTDDFKGRVTITTDTSTSTAYMELSSLRSEDTAVYYCARGGYDGRGFDYWGQGTLVTVSS</t>
+          <t>CN1N=Nc2c(C(N)=O)ncn2C1=O</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -922,7 +921,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Alzheimer's Disease</t>
+          <t>Glioblastoma multiforme (GBM)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -947,11 +946,7 @@
           <t>Target Protein</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Amyloid-β protofibrils</t>
-        </is>
-      </c>
+      <c r="B9" s="6" t="n"/>
       <c r="C9" s="7" t="inlineStr">
         <is>
           <t>e.g. Amyloid-β protofibrils</t>
@@ -969,11 +964,7 @@
           <t>Target PDB ID</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>7Y1Y</t>
-        </is>
-      </c>
+      <c r="B10" s="6" t="n"/>
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>4-character RCSB PDB code</t>
@@ -997,7 +988,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.1</v>
+        <v>30</v>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -1021,10 +1012,8 @@
           <t>Clinical Phase</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B12" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -1050,7 +1039,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2023-01-06</t>
+          <t>1999-08-11</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1083,7 +1072,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>143000</v>
+        <v>194.1</v>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
@@ -1286,7 +1275,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
@@ -1314,11 +1302,7 @@
           <t>Drug Name</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Temozolomide</t>
-        </is>
-      </c>
+      <c r="B30" s="6" t="n"/>
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>e.g. Temozolomide</t>
@@ -1341,11 +1325,7 @@
           <t>Molecule Class</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>small_molecule</t>
-        </is>
-      </c>
+      <c r="B31" s="6" t="n"/>
       <c r="C31" s="7" t="inlineStr">
         <is>
           <t>small_molecule | biologic | peptide</t>
@@ -1363,11 +1343,7 @@
           <t>Molecule Input (SMILES / FASTA / PDB / InChIKey)</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>CN1N=Nc2c(C(N)=O)ncn2C1=O</t>
-        </is>
-      </c>
+      <c r="B32" s="6" t="n"/>
       <c r="C32" s="7" t="inlineStr">
         <is>
           <t>SMILES or sequence</t>
@@ -1390,11 +1366,7 @@
           <t>Indication</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Glioblastoma multiforme (GBM)</t>
-        </is>
-      </c>
+      <c r="B33" s="6" t="n"/>
       <c r="C33" s="7" t="inlineStr">
         <is>
           <t>e.g. Glioblastoma</t>
@@ -1412,9 +1384,7 @@
           <t>Native BBB %</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n">
-        <v>30</v>
-      </c>
+      <c r="B34" s="6" t="n"/>
       <c r="C34" s="7" t="inlineStr">
         <is>
           <t>0-100</t>
@@ -1437,11 +1407,7 @@
           <t>Clinical Phase</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="B35" s="6" t="n"/>
       <c r="C35" s="7" t="inlineStr">
         <is>
           <t>4 | 3 | 2 | 1 | preclinical</t>
@@ -1471,11 +1437,7 @@
           <t>Drug Name</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Nusinersen</t>
-        </is>
-      </c>
+      <c r="B37" s="6" t="n"/>
       <c r="C37" s="7" t="inlineStr">
         <is>
           <t>e.g. Nusinersen</t>
@@ -1498,11 +1460,7 @@
           <t>Molecule Class</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>oligonucleotide</t>
-        </is>
-      </c>
+      <c r="B38" s="6" t="n"/>
       <c r="C38" s="7" t="inlineStr">
         <is>
           <t>oligonucleotide | small_molecule | biologic</t>
@@ -1525,11 +1483,7 @@
           <t>Molecule Input (SMILES / FASTA / sequence / InChIKey)</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>TCACTTTCATAATGCTGG</t>
-        </is>
-      </c>
+      <c r="B39" s="6" t="n"/>
       <c r="C39" s="7" t="inlineStr">
         <is>
           <t>DNA/RNA sequence (5' → 3')</t>
@@ -1552,11 +1506,7 @@
           <t>Indication</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Spinal Muscular Atrophy (SMA)</t>
-        </is>
-      </c>
+      <c r="B40" s="6" t="n"/>
       <c r="C40" s="7" t="inlineStr">
         <is>
           <t>e.g. SMA</t>
@@ -1574,9 +1524,7 @@
           <t>Native BBB %</t>
         </is>
       </c>
-      <c r="B41" s="6" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="B41" s="6" t="n"/>
       <c r="C41" s="7" t="inlineStr">
         <is>
           <t>0-100</t>
@@ -1599,11 +1547,7 @@
           <t>Clinical Phase</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="B42" s="6" t="n"/>
       <c r="C42" s="7" t="inlineStr">
         <is>
           <t>4 | 3 | 2 | 1 | preclinical</t>
